--- a/artfynd/A 15654-2023 artfynd.xlsx
+++ b/artfynd/A 15654-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15654-2023 artfynd.xlsx
+++ b/artfynd/A 15654-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108941841</v>
+        <v>110194590</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1637</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Cylinderskägglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Usnea cylindrica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Clerc</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>G3, Vb</t>
+          <t>G4, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>764931.0178255336</v>
+        <v>764940</v>
       </c>
       <c r="R2" t="n">
-        <v>7086639.824720179</v>
+        <v>7086667</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,26 +779,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Isak Falk Eliasson, Isak Edström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108945306</v>
+        <v>108905250</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -825,14 +818,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>G7, Vb</t>
+          <t>SkäggImplexa, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764943.9218485239</v>
+        <v>764951</v>
       </c>
       <c r="R3" t="n">
-        <v>7086870.795708124</v>
+        <v>7086882</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -859,22 +852,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,16 +897,11 @@
         <v>108940556</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -942,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764914.8180731689</v>
+        <v>764915</v>
       </c>
       <c r="R4" t="n">
-        <v>7086789.342726215</v>
+        <v>7086789</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,19 +1002,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108942927</v>
+        <v>108941841</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,14 +1034,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>G6, Vb</t>
+          <t>G3, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>764915.8815138265</v>
+        <v>764931</v>
       </c>
       <c r="R5" t="n">
-        <v>7086561.322769921</v>
+        <v>7086639</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1073,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1083,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,6 +1107,330 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108941906</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>G4, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>764940</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7086667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108942927</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>G6, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>764915</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7086562</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>108945306</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>G7, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>764944</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7086870</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15654-2023 artfynd.xlsx
+++ b/artfynd/A 15654-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110194590</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108905250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108940556</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108941841</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108941906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108942927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,8 +1466,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108945306</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>